--- a/verification/cases/roundtrip/xlookup/init.xlsx
+++ b/verification/cases/roundtrip/xlookup/init.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B4A6484-F9D1-4224-911A-56A97A418B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD831626-9321-425B-A3DD-1FC0569D85D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -161,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,9 +216,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -251,7 +256,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -357,7 +362,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -508,13 +513,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>8389</v>
       </c>
@@ -537,7 +542,7 @@
         <v>Finance</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>0</v>
       </c>
@@ -548,7 +553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4390</v>
       </c>
@@ -559,7 +564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>8604</v>
       </c>
@@ -570,7 +575,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:4">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>8389</v>
       </c>
@@ -581,7 +586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:4">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>4937</v>
       </c>
@@ -592,7 +597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:4">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>8299</v>
       </c>
@@ -603,7 +608,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:4">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2643</v>
       </c>
@@ -614,7 +619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:4">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>5243</v>
       </c>
@@ -625,7 +630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:4">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9693</v>
       </c>
@@ -636,7 +641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:4">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1636</v>
       </c>
@@ -647,7 +652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:4">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>6703</v>
       </c>
@@ -666,9 +671,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725D2DCE-BC03-4750-9169-7FB311B4807C}">
   <dimension ref="B1:F17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:6">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>19</v>
       </c>
@@ -682,7 +687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>0.1</v>
       </c>
@@ -697,7 +702,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>0.22</v>
       </c>
@@ -708,7 +713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>0.24</v>
       </c>
@@ -719,7 +724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>0.32</v>
       </c>
@@ -727,7 +732,7 @@
         <v>160726</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>0.35</v>
       </c>
@@ -735,7 +740,7 @@
         <v>204100</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>0.37</v>
       </c>
@@ -743,7 +748,7 @@
         <v>510300</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -757,7 +762,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>0.37</v>
       </c>
@@ -772,7 +777,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>0.35</v>
       </c>
@@ -780,7 +785,7 @@
         <v>204100</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>0.32</v>
       </c>
@@ -788,7 +793,7 @@
         <v>160726</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>0.24</v>
       </c>
@@ -796,7 +801,7 @@
         <v>84200</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>0.22</v>
       </c>
@@ -804,7 +809,7 @@
         <v>39475</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>0.1</v>
       </c>
@@ -820,13 +825,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B33508-EDAF-4625-A9AE-AD19E278C510}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>25</v>
       </c>
@@ -840,7 +845,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>28</v>
       </c>
@@ -848,7 +853,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -863,7 +868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>31</v>
       </c>
@@ -871,7 +876,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>32</v>
       </c>
@@ -879,7 +884,7 @@
         <v>15901</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>33</v>
       </c>
@@ -887,7 +892,7 @@
         <v>13801</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -895,7 +900,7 @@
         <v>12181</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>34</v>
       </c>
